--- a/docs/modules/bsee/analysis/production/FDAS_V30/wti_monthly.xlsx
+++ b/docs/modules/bsee/analysis/production/FDAS_V30/wti_monthly.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f9c9cfd5dcd705/Roy/FDAS/Mktg/1-World Oil/2025 article/Economics/article/Lower Tertiary/Final Financials/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_E5BA4605E671D03234FE31D2F8375B06B493737E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1167ABD-B584-466F-A6D9-649B3E82BCDB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1455" windowWidth="19455" windowHeight="13095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -31,8 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,36 +81,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -151,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -185,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -396,3819 +380,3896 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B476"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.85546875" style="3" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B486"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
         <v>31413</v>
       </c>
       <c r="B2">
         <v>22.93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
         <v>31444</v>
       </c>
       <c r="B3">
         <v>15.46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
         <v>31472</v>
       </c>
       <c r="B4">
         <v>12.61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
         <v>31503</v>
       </c>
       <c r="B5">
         <v>12.84</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
         <v>31533</v>
       </c>
       <c r="B6">
         <v>15.38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
         <v>31564</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
         <v>31594</v>
       </c>
       <c r="B8">
         <v>11.59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
         <v>31625</v>
       </c>
       <c r="B9">
         <v>15.1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
         <v>31656</v>
       </c>
       <c r="B10">
         <v>14.87</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
         <v>31686</v>
       </c>
       <c r="B11">
         <v>14.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
         <v>31717</v>
       </c>
       <c r="B12">
         <v>15.22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
         <v>31747</v>
       </c>
       <c r="B13">
         <v>16.11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
         <v>31778</v>
       </c>
       <c r="B14">
-        <v>18.649999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+        <v>18.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
         <v>31809</v>
       </c>
       <c r="B15">
         <v>17.75</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
         <v>31837</v>
       </c>
       <c r="B16">
         <v>18.3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
         <v>31868</v>
       </c>
       <c r="B17">
         <v>18.68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
         <v>31898</v>
       </c>
       <c r="B18">
-        <v>19.440000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+        <v>19.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
         <v>31929</v>
       </c>
       <c r="B19">
         <v>20.07</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
         <v>31959</v>
       </c>
       <c r="B20">
         <v>21.34</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
         <v>31990</v>
       </c>
       <c r="B21">
-        <v>20.309999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+        <v>20.31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
         <v>32021</v>
       </c>
       <c r="B22">
         <v>19.53</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
         <v>32051</v>
       </c>
       <c r="B23">
         <v>19.86</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
         <v>32082</v>
       </c>
       <c r="B24">
-        <v>18.850000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+        <v>18.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
         <v>32112</v>
       </c>
       <c r="B25">
         <v>17.28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
         <v>32143</v>
       </c>
       <c r="B26">
         <v>17.13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
         <v>32174</v>
       </c>
       <c r="B27">
         <v>16.8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" spans="1:2">
+      <c r="A28" s="2">
         <v>32203</v>
       </c>
       <c r="B28">
         <v>16.2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:2">
+      <c r="A29" s="2">
         <v>32234</v>
       </c>
       <c r="B29">
         <v>17.86</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="30" spans="1:2">
+      <c r="A30" s="2">
         <v>32264</v>
       </c>
       <c r="B30">
-        <v>17.420000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+        <v>17.42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2">
         <v>32295</v>
       </c>
       <c r="B31">
         <v>16.53</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="32" spans="1:2">
+      <c r="A32" s="2">
         <v>32325</v>
       </c>
       <c r="B32">
         <v>15.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="33" spans="1:2">
+      <c r="A33" s="2">
         <v>32356</v>
       </c>
       <c r="B33">
         <v>15.52</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" spans="1:2">
+      <c r="A34" s="2">
         <v>32387</v>
       </c>
       <c r="B34">
         <v>14.54</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
         <v>32417</v>
       </c>
       <c r="B35">
         <v>13.77</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
         <v>32448</v>
       </c>
       <c r="B36">
         <v>14.14</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
         <v>32478</v>
       </c>
       <c r="B37">
         <v>16.38</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
         <v>32509</v>
       </c>
       <c r="B38">
         <v>18.02</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
         <v>32540</v>
       </c>
       <c r="B39">
-        <v>17.940000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+        <v>17.94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
         <v>32568</v>
       </c>
       <c r="B40">
         <v>19.48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
         <v>32599</v>
       </c>
       <c r="B41">
         <v>21.07</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
         <v>32629</v>
       </c>
       <c r="B42">
         <v>20.12</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
         <v>32660</v>
       </c>
       <c r="B43">
         <v>20.05</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
         <v>32690</v>
       </c>
       <c r="B44">
         <v>19.78</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
         <v>32721</v>
       </c>
       <c r="B45">
-        <v>18.579999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+        <v>18.58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
         <v>32752</v>
       </c>
       <c r="B46">
         <v>19.59</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
         <v>32782</v>
       </c>
       <c r="B47">
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
         <v>32813</v>
       </c>
       <c r="B48">
         <v>19.86</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
         <v>32843</v>
       </c>
       <c r="B49">
         <v>21.1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
         <v>32874</v>
       </c>
       <c r="B50">
         <v>22.86</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
         <v>32905</v>
       </c>
       <c r="B51">
         <v>22.11</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
         <v>32933</v>
       </c>
       <c r="B52">
         <v>20.39</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
         <v>32964</v>
       </c>
       <c r="B53">
         <v>18.43</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
         <v>32994</v>
       </c>
       <c r="B54">
         <v>18.2</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
         <v>33025</v>
       </c>
       <c r="B55">
         <v>16.7</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
         <v>33055</v>
       </c>
       <c r="B56">
         <v>18.45</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
         <v>33086</v>
       </c>
       <c r="B57">
         <v>27.31</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
         <v>33117</v>
       </c>
       <c r="B58">
         <v>33.51</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
         <v>33147</v>
       </c>
       <c r="B59">
         <v>36.04</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
         <v>33178</v>
       </c>
       <c r="B60">
         <v>32.33</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" spans="1:2">
+      <c r="A61" s="2">
         <v>33208</v>
       </c>
       <c r="B61">
         <v>27.28</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="62" spans="1:2">
+      <c r="A62" s="2">
         <v>33239</v>
       </c>
       <c r="B62">
         <v>25.23</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" spans="1:2">
+      <c r="A63" s="2">
         <v>33270</v>
       </c>
       <c r="B63">
         <v>20.48</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="64" spans="1:2">
+      <c r="A64" s="2">
         <v>33298</v>
       </c>
       <c r="B64">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2">
         <v>33329</v>
       </c>
       <c r="B65">
         <v>20.83</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
         <v>33359</v>
       </c>
       <c r="B66">
         <v>21.23</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
         <v>33390</v>
       </c>
       <c r="B67">
-        <v>20.190000000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+        <v>20.19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
         <v>33420</v>
       </c>
       <c r="B68">
         <v>21.4</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
         <v>33451</v>
       </c>
       <c r="B69">
         <v>21.69</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="70" spans="1:2">
+      <c r="A70" s="2">
         <v>33482</v>
       </c>
       <c r="B70">
         <v>21.89</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="71" spans="1:2">
+      <c r="A71" s="2">
         <v>33512</v>
       </c>
       <c r="B71">
         <v>23.23</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="72" spans="1:2">
+      <c r="A72" s="2">
         <v>33543</v>
       </c>
       <c r="B72">
         <v>22.46</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+    <row r="73" spans="1:2">
+      <c r="A73" s="2">
         <v>33573</v>
       </c>
       <c r="B73">
         <v>19.5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+    <row r="74" spans="1:2">
+      <c r="A74" s="2">
         <v>33604</v>
       </c>
       <c r="B74">
         <v>18.79</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+    <row r="75" spans="1:2">
+      <c r="A75" s="2">
         <v>33635</v>
       </c>
       <c r="B75">
-        <v>19.010000000000002</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+        <v>19.01</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
         <v>33664</v>
       </c>
       <c r="B76">
-        <v>18.920000000000002</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+        <v>18.92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2">
         <v>33695</v>
       </c>
       <c r="B77">
         <v>20.23</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+    <row r="78" spans="1:2">
+      <c r="A78" s="2">
         <v>33725</v>
       </c>
       <c r="B78">
         <v>20.98</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+    <row r="79" spans="1:2">
+      <c r="A79" s="2">
         <v>33756</v>
       </c>
       <c r="B79">
         <v>22.39</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+    <row r="80" spans="1:2">
+      <c r="A80" s="2">
         <v>33786</v>
       </c>
       <c r="B80">
         <v>21.78</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
         <v>33817</v>
       </c>
       <c r="B81">
         <v>21.34</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
         <v>33848</v>
       </c>
       <c r="B82">
         <v>21.88</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
         <v>33878</v>
       </c>
       <c r="B83">
         <v>21.69</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
         <v>33909</v>
       </c>
       <c r="B84">
         <v>20.34</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
         <v>33939</v>
       </c>
       <c r="B85">
         <v>19.41</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+    <row r="86" spans="1:2">
+      <c r="A86" s="2">
         <v>33970</v>
       </c>
       <c r="B86">
         <v>19.03</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
+    <row r="87" spans="1:2">
+      <c r="A87" s="2">
         <v>34001</v>
       </c>
       <c r="B87">
         <v>20.09</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
+    <row r="88" spans="1:2">
+      <c r="A88" s="2">
         <v>34029</v>
       </c>
       <c r="B88">
         <v>20.32</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
         <v>34060</v>
       </c>
       <c r="B89">
         <v>20.25</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
         <v>34090</v>
       </c>
       <c r="B90">
         <v>19.95</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
         <v>34121</v>
       </c>
       <c r="B91">
         <v>19.09</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
         <v>34151</v>
       </c>
       <c r="B92">
         <v>17.89</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
         <v>34182</v>
       </c>
       <c r="B93">
-        <v>18.010000000000002</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
         <v>34213</v>
       </c>
       <c r="B94">
         <v>17.5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
         <v>34243</v>
       </c>
       <c r="B95">
-        <v>18.149999999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
         <v>34274</v>
       </c>
       <c r="B96">
         <v>16.61</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
         <v>34304</v>
       </c>
       <c r="B97">
         <v>14.52</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>34335</v>
       </c>
       <c r="B98">
         <v>15.03</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
         <v>34366</v>
       </c>
       <c r="B99">
         <v>14.78</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
         <v>34394</v>
       </c>
       <c r="B100">
         <v>14.68</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
         <v>34425</v>
       </c>
       <c r="B101">
-        <v>16.420000000000002</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
         <v>34455</v>
       </c>
       <c r="B102">
         <v>17.89</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
         <v>34486</v>
       </c>
       <c r="B103">
-        <v>19.059999999999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
         <v>34516</v>
       </c>
       <c r="B104">
         <v>19.66</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
         <v>34547</v>
       </c>
       <c r="B105">
         <v>18.38</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
         <v>34578</v>
       </c>
       <c r="B106">
         <v>17.45</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
         <v>34608</v>
       </c>
       <c r="B107">
         <v>17.72</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
         <v>34639</v>
       </c>
       <c r="B108">
         <v>18.07</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
         <v>34669</v>
       </c>
       <c r="B109">
         <v>17.16</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
         <v>34700</v>
       </c>
       <c r="B110">
         <v>18.04</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
         <v>34731</v>
       </c>
       <c r="B111">
         <v>18.57</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
         <v>34759</v>
       </c>
       <c r="B112">
         <v>18.54</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
         <v>34790</v>
       </c>
       <c r="B113">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
         <v>34820</v>
       </c>
       <c r="B114">
-        <v>19.739999999999998</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+        <v>19.74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
         <v>34851</v>
       </c>
       <c r="B115">
         <v>18.45</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
         <v>34881</v>
       </c>
       <c r="B116">
-        <v>17.329999999999998</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+        <v>17.33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
         <v>34912</v>
       </c>
       <c r="B117">
         <v>18.02</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
         <v>34943</v>
       </c>
       <c r="B118">
         <v>18.23</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
         <v>34973</v>
       </c>
       <c r="B119">
         <v>17.43</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
         <v>35004</v>
       </c>
       <c r="B120">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
         <v>35034</v>
       </c>
       <c r="B121">
         <v>19.03</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
         <v>35065</v>
       </c>
       <c r="B122">
         <v>18.86</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
         <v>35096</v>
       </c>
       <c r="B123">
         <v>19.09</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
         <v>35125</v>
       </c>
       <c r="B124">
         <v>21.33</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
         <v>35156</v>
       </c>
       <c r="B125">
         <v>23.5</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
         <v>35186</v>
       </c>
       <c r="B126">
         <v>21.17</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
         <v>35217</v>
       </c>
       <c r="B127">
-        <v>20.420000000000002</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
+        <v>20.42</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
         <v>35247</v>
       </c>
       <c r="B128">
         <v>21.3</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="3">
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
         <v>35278</v>
       </c>
       <c r="B129">
         <v>21.9</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
         <v>35309</v>
       </c>
       <c r="B130">
         <v>23.97</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
         <v>35339</v>
       </c>
       <c r="B131">
         <v>24.88</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
         <v>35370</v>
       </c>
       <c r="B132">
         <v>23.71</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
         <v>35400</v>
       </c>
       <c r="B133">
         <v>25.23</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
         <v>35431</v>
       </c>
       <c r="B134">
         <v>25.13</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
         <v>35462</v>
       </c>
       <c r="B135">
         <v>22.18</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
         <v>35490</v>
       </c>
       <c r="B136">
         <v>20.97</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
         <v>35521</v>
       </c>
       <c r="B137">
         <v>19.7</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="3">
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
         <v>35551</v>
       </c>
       <c r="B138">
         <v>20.82</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="3">
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
         <v>35582</v>
       </c>
       <c r="B139">
-        <v>19.260000000000002</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="3">
+        <v>19.26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
         <v>35612</v>
       </c>
       <c r="B140">
         <v>19.66</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="3">
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
         <v>35643</v>
       </c>
       <c r="B141">
         <v>19.95</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
         <v>35674</v>
       </c>
       <c r="B142">
         <v>19.8</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="3">
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
         <v>35704</v>
       </c>
       <c r="B143">
         <v>21.33</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="3">
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
         <v>35735</v>
       </c>
       <c r="B144">
-        <v>20.190000000000001</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="3">
+        <v>20.19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
         <v>35765</v>
       </c>
       <c r="B145">
-        <v>18.329999999999998</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="3">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
         <v>35796</v>
       </c>
       <c r="B146">
         <v>16.72</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="3">
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
         <v>35827</v>
       </c>
       <c r="B147">
-        <v>16.059999999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
         <v>35855</v>
       </c>
       <c r="B148">
         <v>15.12</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="3">
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
         <v>35886</v>
       </c>
       <c r="B149">
         <v>15.35</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="3">
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
         <v>35916</v>
       </c>
       <c r="B150">
         <v>14.91</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="3">
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
         <v>35947</v>
       </c>
       <c r="B151">
         <v>13.72</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="3">
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
         <v>35977</v>
       </c>
       <c r="B152">
         <v>14.17</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="3">
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
         <v>36008</v>
       </c>
       <c r="B153">
         <v>13.47</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="3">
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
         <v>36039</v>
       </c>
       <c r="B154">
         <v>15.03</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="3">
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
         <v>36069</v>
       </c>
       <c r="B155">
         <v>14.46</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="3">
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
         <v>36100</v>
       </c>
       <c r="B156">
         <v>13</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="3">
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
         <v>36130</v>
       </c>
       <c r="B157">
         <v>11.35</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
         <v>36161</v>
       </c>
       <c r="B158">
         <v>12.52</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
         <v>36192</v>
       </c>
       <c r="B159">
         <v>12.01</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
         <v>36220</v>
       </c>
       <c r="B160">
         <v>14.68</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
         <v>36251</v>
       </c>
       <c r="B161">
-        <v>17.309999999999999</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="3">
+        <v>17.31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
         <v>36281</v>
       </c>
       <c r="B162">
         <v>17.72</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="3">
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
         <v>36312</v>
       </c>
       <c r="B163">
-        <v>17.920000000000002</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="3">
+        <v>17.92</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
         <v>36342</v>
       </c>
       <c r="B164">
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="3">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
         <v>36373</v>
       </c>
       <c r="B165">
         <v>21.28</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="3">
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
         <v>36404</v>
       </c>
       <c r="B166">
         <v>23.8</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="3">
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
         <v>36434</v>
       </c>
       <c r="B167">
         <v>22.69</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="3">
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
         <v>36465</v>
       </c>
       <c r="B168">
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="3">
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
         <v>36495</v>
       </c>
       <c r="B169">
         <v>26.1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="3">
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
         <v>36526</v>
       </c>
       <c r="B170">
         <v>27.26</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="3">
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
         <v>36557</v>
       </c>
       <c r="B171">
         <v>29.37</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="3">
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
         <v>36586</v>
       </c>
       <c r="B172">
         <v>29.84</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="3">
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
         <v>36617</v>
       </c>
       <c r="B173">
         <v>25.72</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="3">
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
         <v>36647</v>
       </c>
       <c r="B174">
         <v>28.79</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="3">
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
         <v>36678</v>
       </c>
       <c r="B175">
         <v>31.82</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
         <v>36708</v>
       </c>
       <c r="B176">
         <v>29.7</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="3">
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
         <v>36739</v>
       </c>
       <c r="B177">
         <v>31.26</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="3">
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
         <v>36770</v>
       </c>
       <c r="B178">
-        <v>33.880000000000003</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="3">
+        <v>33.88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
         <v>36800</v>
       </c>
       <c r="B179">
         <v>33.11</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="3">
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
         <v>36831</v>
       </c>
       <c r="B180">
         <v>34.42</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="3">
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
         <v>36861</v>
       </c>
       <c r="B181">
         <v>28.44</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="3">
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
         <v>36892</v>
       </c>
       <c r="B182">
         <v>29.59</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="3">
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
         <v>36923</v>
       </c>
       <c r="B183">
         <v>29.61</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="3">
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
         <v>36951</v>
       </c>
       <c r="B184">
         <v>27.25</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="3">
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
         <v>36982</v>
       </c>
       <c r="B185">
         <v>27.49</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="3">
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
         <v>37012</v>
       </c>
       <c r="B186">
         <v>28.63</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="3">
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
         <v>37043</v>
       </c>
       <c r="B187">
         <v>27.6</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="3">
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
         <v>37073</v>
       </c>
       <c r="B188">
         <v>26.43</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="3">
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
         <v>37104</v>
       </c>
       <c r="B189">
         <v>27.37</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="3">
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
         <v>37135</v>
       </c>
       <c r="B190">
         <v>26.2</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="3">
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
         <v>37165</v>
       </c>
       <c r="B191">
         <v>22.17</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="3">
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
         <v>37196</v>
       </c>
       <c r="B192">
         <v>19.64</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="3">
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
         <v>37226</v>
       </c>
       <c r="B193">
         <v>19.39</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" s="3">
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
         <v>37257</v>
       </c>
       <c r="B194">
         <v>19.72</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="3">
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
         <v>37288</v>
       </c>
       <c r="B195">
         <v>20.72</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="3">
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
         <v>37316</v>
       </c>
       <c r="B196">
         <v>24.53</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="3">
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
         <v>37347</v>
       </c>
       <c r="B197">
         <v>26.18</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="3">
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
         <v>37377</v>
       </c>
       <c r="B198">
         <v>27.04</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="3">
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
         <v>37408</v>
       </c>
       <c r="B199">
         <v>25.52</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="3">
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
         <v>37438</v>
       </c>
       <c r="B200">
         <v>26.97</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="3">
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
         <v>37469</v>
       </c>
       <c r="B201">
         <v>28.39</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" s="3">
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
         <v>37500</v>
       </c>
       <c r="B202">
         <v>29.66</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="3">
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
         <v>37530</v>
       </c>
       <c r="B203">
         <v>28.84</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="3">
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
         <v>37561</v>
       </c>
       <c r="B204">
         <v>26.35</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="3">
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
         <v>37591</v>
       </c>
       <c r="B205">
         <v>29.46</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="3">
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
         <v>37622</v>
       </c>
       <c r="B206">
-        <v>32.950000000000003</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="3">
+        <v>32.95</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
         <v>37653</v>
       </c>
       <c r="B207">
         <v>35.83</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" s="3">
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
         <v>37681</v>
       </c>
       <c r="B208">
         <v>33.51</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" s="3">
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
         <v>37712</v>
       </c>
       <c r="B209">
         <v>28.17</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" s="3">
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
         <v>37742</v>
       </c>
       <c r="B210">
         <v>28.11</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" s="3">
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
         <v>37773</v>
       </c>
       <c r="B211">
         <v>30.66</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="3">
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
         <v>37803</v>
       </c>
       <c r="B212">
         <v>30.76</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="3">
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
         <v>37834</v>
       </c>
       <c r="B213">
         <v>31.57</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="3">
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
         <v>37865</v>
       </c>
       <c r="B214">
         <v>28.31</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="3">
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
         <v>37895</v>
       </c>
       <c r="B215">
         <v>30.34</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="3">
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
         <v>37926</v>
       </c>
       <c r="B216">
         <v>31.11</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="3">
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
         <v>37956</v>
       </c>
       <c r="B217">
-        <v>32.130000000000003</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" s="3">
+        <v>32.13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
         <v>37987</v>
       </c>
       <c r="B218">
         <v>34.31</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" s="3">
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
         <v>38018</v>
       </c>
       <c r="B219">
         <v>34.69</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="3">
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
         <v>38047</v>
       </c>
       <c r="B220">
         <v>36.74</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="3">
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
         <v>38078</v>
       </c>
       <c r="B221">
         <v>36.75</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="3">
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
         <v>38108</v>
       </c>
       <c r="B222">
         <v>40.28</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="3">
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
         <v>38139</v>
       </c>
       <c r="B223">
         <v>38.03</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="3">
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
         <v>38169</v>
       </c>
       <c r="B224">
         <v>40.78</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="3">
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
         <v>38200</v>
       </c>
       <c r="B225">
         <v>44.9</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="3">
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
         <v>38231</v>
       </c>
       <c r="B226">
         <v>45.94</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" s="3">
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
         <v>38261</v>
       </c>
       <c r="B227">
         <v>53.28</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="3">
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
         <v>38292</v>
       </c>
       <c r="B228">
         <v>48.47</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="3">
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
         <v>38322</v>
       </c>
       <c r="B229">
         <v>43.15</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" s="3">
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
         <v>38353</v>
       </c>
       <c r="B230">
         <v>46.84</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" s="3">
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
         <v>38384</v>
       </c>
       <c r="B231">
         <v>48.15</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" s="3">
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
         <v>38412</v>
       </c>
       <c r="B232">
         <v>54.19</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" s="3">
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
         <v>38443</v>
       </c>
       <c r="B233">
         <v>52.98</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" s="3">
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
         <v>38473</v>
       </c>
       <c r="B234">
         <v>49.83</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" s="3">
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
         <v>38504</v>
       </c>
       <c r="B235">
         <v>56.35</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" s="3">
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
         <v>38534</v>
       </c>
       <c r="B236">
         <v>59</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" s="3">
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
         <v>38565</v>
       </c>
       <c r="B237">
-        <v>64.989999999999995</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" s="3">
+        <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
         <v>38596</v>
       </c>
       <c r="B238">
         <v>65.59</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" s="3">
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
         <v>38626</v>
       </c>
       <c r="B239">
         <v>62.26</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" s="3">
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
         <v>38657</v>
       </c>
       <c r="B240">
         <v>58.32</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" s="3">
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
         <v>38687</v>
       </c>
       <c r="B241">
         <v>59.41</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" s="3">
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
         <v>38718</v>
       </c>
       <c r="B242">
-        <v>65.489999999999995</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" s="3">
+        <v>65.48999999999999</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
         <v>38749</v>
       </c>
       <c r="B243">
         <v>61.63</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" s="3">
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
         <v>38777</v>
       </c>
       <c r="B244">
         <v>62.69</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="3">
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
         <v>38808</v>
       </c>
       <c r="B245">
         <v>69.44</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" s="3">
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
         <v>38838</v>
       </c>
       <c r="B246">
         <v>70.84</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" s="3">
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
         <v>38869</v>
       </c>
       <c r="B247">
         <v>70.95</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" s="3">
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
         <v>38899</v>
       </c>
       <c r="B248">
         <v>74.41</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" s="3">
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
         <v>38930</v>
       </c>
       <c r="B249">
-        <v>73.040000000000006</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" s="3">
+        <v>73.04000000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
         <v>38961</v>
       </c>
       <c r="B250">
         <v>63.8</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" s="3">
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
         <v>38991</v>
       </c>
       <c r="B251">
         <v>58.89</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" s="3">
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
         <v>39022</v>
       </c>
       <c r="B252">
         <v>59.08</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="3">
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
         <v>39052</v>
       </c>
       <c r="B253">
         <v>61.96</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" s="3">
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
         <v>39083</v>
       </c>
       <c r="B254">
         <v>54.51</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" s="3">
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
         <v>39114</v>
       </c>
       <c r="B255">
         <v>59.28</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" s="3">
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
         <v>39142</v>
       </c>
       <c r="B256">
         <v>60.44</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" s="3">
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
         <v>39173</v>
       </c>
       <c r="B257">
         <v>63.98</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258" s="3">
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
         <v>39203</v>
       </c>
       <c r="B258">
         <v>63.46</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259" s="3">
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
         <v>39234</v>
       </c>
       <c r="B259">
-        <v>67.489999999999995</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260" s="3">
+        <v>67.48999999999999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
         <v>39264</v>
       </c>
       <c r="B260">
         <v>74.12</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261" s="3">
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
         <v>39295</v>
       </c>
       <c r="B261">
         <v>72.36</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262" s="3">
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
         <v>39326</v>
       </c>
       <c r="B262">
         <v>79.92</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263" s="3">
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
         <v>39356</v>
       </c>
       <c r="B263">
         <v>85.8</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="3">
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
         <v>39387</v>
       </c>
       <c r="B264">
         <v>94.77</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="3">
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
         <v>39417</v>
       </c>
       <c r="B265">
         <v>91.69</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="3">
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
         <v>39448</v>
       </c>
       <c r="B266">
         <v>92.97</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="3">
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
         <v>39479</v>
       </c>
       <c r="B267">
         <v>95.39</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="3">
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
         <v>39508</v>
       </c>
       <c r="B268">
         <v>105.45</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="3">
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
         <v>39539</v>
       </c>
       <c r="B269">
         <v>112.58</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="3">
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
         <v>39569</v>
       </c>
       <c r="B270">
         <v>125.4</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="3">
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
         <v>39600</v>
       </c>
       <c r="B271">
         <v>133.88</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="3">
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
         <v>39630</v>
       </c>
       <c r="B272">
         <v>133.37</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="3">
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
         <v>39661</v>
       </c>
       <c r="B273">
         <v>116.67</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="3">
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
         <v>39692</v>
       </c>
       <c r="B274">
         <v>104.11</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="3">
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
         <v>39722</v>
       </c>
       <c r="B275">
         <v>76.61</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="3">
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
         <v>39753</v>
       </c>
       <c r="B276">
         <v>57.31</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="3">
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
         <v>39783</v>
       </c>
       <c r="B277">
         <v>41.12</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="3">
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
         <v>39814</v>
       </c>
       <c r="B278">
         <v>41.71</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="3">
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
         <v>39845</v>
       </c>
       <c r="B279">
-        <v>39.090000000000003</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="3">
+        <v>39.09</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
         <v>39873</v>
       </c>
       <c r="B280">
         <v>47.94</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="3">
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
         <v>39904</v>
       </c>
       <c r="B281">
         <v>49.65</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282" s="3">
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
         <v>39934</v>
       </c>
       <c r="B282">
         <v>59.03</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283" s="3">
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
         <v>39965</v>
       </c>
       <c r="B283">
         <v>69.64</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284" s="3">
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
         <v>39995</v>
       </c>
       <c r="B284">
-        <v>64.150000000000006</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285" s="3">
+        <v>64.15000000000001</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
         <v>40026</v>
       </c>
       <c r="B285">
         <v>71.05</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286" s="3">
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
         <v>40057</v>
       </c>
       <c r="B286">
         <v>69.41</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287" s="3">
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
         <v>40087</v>
       </c>
       <c r="B287">
         <v>75.72</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288" s="3">
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
         <v>40118</v>
       </c>
       <c r="B288">
-        <v>77.989999999999995</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289" s="3">
+        <v>77.98999999999999</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
         <v>40148</v>
       </c>
       <c r="B289">
         <v>74.47</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290" s="3">
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
         <v>40179</v>
       </c>
       <c r="B290">
         <v>78.33</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" s="3">
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
         <v>40210</v>
       </c>
       <c r="B291">
         <v>76.39</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" s="3">
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
         <v>40238</v>
       </c>
       <c r="B292">
         <v>81.2</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" s="3">
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
         <v>40269</v>
       </c>
       <c r="B293">
-        <v>84.29</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" s="3">
+        <v>84.29000000000001</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
         <v>40299</v>
       </c>
       <c r="B294">
-        <v>73.739999999999995</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" s="3">
+        <v>73.73999999999999</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
         <v>40330</v>
       </c>
       <c r="B295">
         <v>75.34</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" s="3">
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
         <v>40360</v>
       </c>
       <c r="B296">
-        <v>76.319999999999993</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" s="3">
+        <v>76.31999999999999</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
         <v>40391</v>
       </c>
       <c r="B297">
-        <v>76.599999999999994</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" s="3">
+        <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
         <v>40422</v>
       </c>
       <c r="B298">
-        <v>75.239999999999995</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" s="3">
+        <v>75.23999999999999</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
         <v>40452</v>
       </c>
       <c r="B299">
         <v>81.89</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" s="3">
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
         <v>40483</v>
       </c>
       <c r="B300">
         <v>84.25</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" s="3">
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
         <v>40513</v>
       </c>
       <c r="B301">
-        <v>89.15</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" s="3">
+        <v>89.15000000000001</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
         <v>40544</v>
       </c>
       <c r="B302">
         <v>89.17</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" s="3">
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
         <v>40575</v>
       </c>
       <c r="B303">
         <v>88.58</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" s="3">
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
         <v>40603</v>
       </c>
       <c r="B304">
         <v>102.86</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" s="3">
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
         <v>40634</v>
       </c>
       <c r="B305">
         <v>109.53</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" s="3">
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
         <v>40664</v>
       </c>
       <c r="B306">
         <v>100.9</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" s="3">
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
         <v>40695</v>
       </c>
       <c r="B307">
-        <v>96.26</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" s="3">
+        <v>96.26000000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
         <v>40725</v>
       </c>
       <c r="B308">
         <v>97.3</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" s="3">
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
         <v>40756</v>
       </c>
       <c r="B309">
         <v>86.33</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" s="3">
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
         <v>40787</v>
       </c>
       <c r="B310">
         <v>85.52</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" s="3">
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
         <v>40817</v>
       </c>
       <c r="B311">
-        <v>86.32</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" s="3">
+        <v>86.31999999999999</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
         <v>40848</v>
       </c>
       <c r="B312">
         <v>97.16</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" s="3">
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
         <v>40878</v>
       </c>
       <c r="B313">
         <v>98.56</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" s="3">
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
         <v>40909</v>
       </c>
       <c r="B314">
         <v>100.27</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" s="3">
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
         <v>40940</v>
       </c>
       <c r="B315">
         <v>102.2</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" s="3">
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
         <v>40969</v>
       </c>
       <c r="B316">
         <v>106.16</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" s="3">
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
         <v>41000</v>
       </c>
       <c r="B317">
         <v>103.32</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" s="3">
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
         <v>41030</v>
       </c>
       <c r="B318">
         <v>94.66</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" s="3">
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
         <v>41061</v>
       </c>
       <c r="B319">
         <v>82.3</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" s="3">
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
         <v>41091</v>
       </c>
       <c r="B320">
-        <v>87.9</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" s="3">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
         <v>41122</v>
       </c>
       <c r="B321">
         <v>94.13</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" s="3">
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
         <v>41153</v>
       </c>
       <c r="B322">
-        <v>94.51</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" s="3">
+        <v>94.51000000000001</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
         <v>41183</v>
       </c>
       <c r="B323">
-        <v>89.49</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" s="3">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
         <v>41214</v>
       </c>
       <c r="B324">
         <v>86.53</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" s="3">
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
         <v>41244</v>
       </c>
       <c r="B325">
         <v>87.86</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" s="3">
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
         <v>41275</v>
       </c>
       <c r="B326">
-        <v>94.76</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" s="3">
+        <v>94.76000000000001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
         <v>41306</v>
       </c>
       <c r="B327">
         <v>95.31</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" s="3">
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
         <v>41334</v>
       </c>
       <c r="B328">
         <v>92.94</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" s="3">
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
         <v>41365</v>
       </c>
       <c r="B329">
         <v>92.02</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" s="3">
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
         <v>41395</v>
       </c>
       <c r="B330">
-        <v>94.51</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" s="3">
+        <v>94.51000000000001</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
         <v>41426</v>
       </c>
       <c r="B331">
         <v>95.77</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" s="3">
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
         <v>41456</v>
       </c>
       <c r="B332">
         <v>104.67</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333" s="3">
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
         <v>41487</v>
       </c>
       <c r="B333">
         <v>106.57</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334" s="3">
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
         <v>41518</v>
       </c>
       <c r="B334">
         <v>106.29</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="3">
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
         <v>41548</v>
       </c>
       <c r="B335">
         <v>100.54</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="3">
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
         <v>41579</v>
       </c>
       <c r="B336">
         <v>93.86</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="3">
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
         <v>41609</v>
       </c>
       <c r="B337">
         <v>97.63</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="3">
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
         <v>41640</v>
       </c>
       <c r="B338">
         <v>94.62</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="3">
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
         <v>41671</v>
       </c>
       <c r="B339">
         <v>100.82</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="3">
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
         <v>41699</v>
       </c>
       <c r="B340">
         <v>100.8</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="3">
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
         <v>41730</v>
       </c>
       <c r="B341">
         <v>102.07</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" s="3">
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
         <v>41760</v>
       </c>
       <c r="B342">
         <v>102.18</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" s="3">
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
         <v>41791</v>
       </c>
       <c r="B343">
         <v>105.79</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" s="3">
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
         <v>41821</v>
       </c>
       <c r="B344">
         <v>103.59</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="3">
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
         <v>41852</v>
       </c>
       <c r="B345">
-        <v>96.54</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" s="3">
+        <v>96.54000000000001</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
         <v>41883</v>
       </c>
       <c r="B346">
-        <v>93.21</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="3">
+        <v>93.20999999999999</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
         <v>41913</v>
       </c>
       <c r="B347">
-        <v>84.4</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" s="3">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
         <v>41944</v>
       </c>
       <c r="B348">
-        <v>75.790000000000006</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" s="3">
+        <v>75.79000000000001</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
         <v>41974</v>
       </c>
       <c r="B349">
         <v>59.29</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="3">
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
         <v>42005</v>
       </c>
       <c r="B350">
         <v>47.22</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351" s="3">
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
         <v>42036</v>
       </c>
       <c r="B351">
         <v>50.58</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352" s="3">
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
         <v>42064</v>
       </c>
       <c r="B352">
         <v>47.82</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353" s="3">
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
         <v>42095</v>
       </c>
       <c r="B353">
         <v>54.45</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354" s="3">
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
         <v>42125</v>
       </c>
       <c r="B354">
         <v>59.27</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355" s="3">
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
         <v>42156</v>
       </c>
       <c r="B355">
         <v>59.82</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356" s="3">
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
         <v>42186</v>
       </c>
       <c r="B356">
         <v>50.9</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357" s="3">
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
         <v>42217</v>
       </c>
       <c r="B357">
         <v>42.87</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358" s="3">
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
         <v>42248</v>
       </c>
       <c r="B358">
         <v>45.48</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359" s="3">
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
         <v>42278</v>
       </c>
       <c r="B359">
         <v>46.22</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360" s="3">
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
         <v>42309</v>
       </c>
       <c r="B360">
         <v>42.44</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361" s="3">
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
         <v>42339</v>
       </c>
       <c r="B361">
         <v>37.19</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362" s="3">
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
         <v>42370</v>
       </c>
       <c r="B362">
         <v>31.68</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363" s="3">
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
         <v>42401</v>
       </c>
       <c r="B363">
         <v>30.32</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364" s="3">
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
         <v>42430</v>
       </c>
       <c r="B364">
-        <v>37.549999999999997</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365" s="3">
+        <v>37.55</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
         <v>42461</v>
       </c>
       <c r="B365">
         <v>40.75</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366" s="3">
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
         <v>42491</v>
       </c>
       <c r="B366">
         <v>46.71</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367" s="3">
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
         <v>42522</v>
       </c>
       <c r="B367">
         <v>48.76</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368" s="3">
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
         <v>42552</v>
       </c>
       <c r="B368">
         <v>44.65</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369" s="3">
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
         <v>42583</v>
       </c>
       <c r="B369">
         <v>44.72</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370" s="3">
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
         <v>42614</v>
       </c>
       <c r="B370">
         <v>45.18</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371" s="3">
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
         <v>42644</v>
       </c>
       <c r="B371">
         <v>49.78</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372" s="3">
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
         <v>42675</v>
       </c>
       <c r="B372">
         <v>45.66</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373" s="3">
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
         <v>42705</v>
       </c>
       <c r="B373">
         <v>51.97</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374" s="3">
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
         <v>42736</v>
       </c>
       <c r="B374">
         <v>52.5</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375" s="3">
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
         <v>42767</v>
       </c>
       <c r="B375">
         <v>53.47</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376" s="3">
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
         <v>42795</v>
       </c>
       <c r="B376">
         <v>49.33</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377" s="3">
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
         <v>42826</v>
       </c>
       <c r="B377">
         <v>51.06</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378" s="3">
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
         <v>42856</v>
       </c>
       <c r="B378">
         <v>48.48</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379" s="3">
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
         <v>42887</v>
       </c>
       <c r="B379">
         <v>45.18</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380" s="3">
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
         <v>42917</v>
       </c>
       <c r="B380">
         <v>46.63</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381" s="3">
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
         <v>42948</v>
       </c>
       <c r="B381">
         <v>48.04</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382" s="3">
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
         <v>42979</v>
       </c>
       <c r="B382">
         <v>49.82</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383" s="3">
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
         <v>43009</v>
       </c>
       <c r="B383">
         <v>51.58</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384" s="3">
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
         <v>43040</v>
       </c>
       <c r="B384">
         <v>56.64</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385" s="3">
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
         <v>43070</v>
       </c>
       <c r="B385">
         <v>57.88</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386" s="3">
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
         <v>43101</v>
       </c>
       <c r="B386">
         <v>63.7</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387" s="3">
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
         <v>43132</v>
       </c>
       <c r="B387">
         <v>62.23</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388" s="3">
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
         <v>43160</v>
       </c>
       <c r="B388">
         <v>62.73</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389" s="3">
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
         <v>43191</v>
       </c>
       <c r="B389">
         <v>66.25</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390" s="3">
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
         <v>43221</v>
       </c>
       <c r="B390">
         <v>69.98</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391" s="3">
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
         <v>43252</v>
       </c>
       <c r="B391">
         <v>67.87</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392" s="3">
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
         <v>43282</v>
       </c>
       <c r="B392">
         <v>70.98</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393" s="3">
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
         <v>43313</v>
       </c>
       <c r="B393">
         <v>68.06</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394" s="3">
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
         <v>43344</v>
       </c>
       <c r="B394">
         <v>70.23</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395" s="3">
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
         <v>43374</v>
       </c>
       <c r="B395">
         <v>70.75</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396" s="3">
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
         <v>43405</v>
       </c>
       <c r="B396">
         <v>56.96</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397" s="3">
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
         <v>43435</v>
       </c>
       <c r="B397">
         <v>49.52</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398" s="3">
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
         <v>43466</v>
       </c>
       <c r="B398">
         <v>51.38</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399" s="3">
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
         <v>43497</v>
       </c>
       <c r="B399">
         <v>54.95</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400" s="3">
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
         <v>43525</v>
       </c>
       <c r="B400">
         <v>58.15</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401" s="3">
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
         <v>43556</v>
       </c>
       <c r="B401">
         <v>63.86</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402" s="3">
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
         <v>43586</v>
       </c>
       <c r="B402">
         <v>60.83</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403" s="3">
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
         <v>43617</v>
       </c>
       <c r="B403">
         <v>54.66</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404" s="3">
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
         <v>43647</v>
       </c>
       <c r="B404">
         <v>57.35</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405" s="3">
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
         <v>43678</v>
       </c>
       <c r="B405">
         <v>54.81</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406" s="3">
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
         <v>43709</v>
       </c>
       <c r="B406">
         <v>56.95</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407" s="3">
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
         <v>43739</v>
       </c>
       <c r="B407">
         <v>53.96</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408" s="3">
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
         <v>43770</v>
       </c>
       <c r="B408">
         <v>57.03</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409" s="3">
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
         <v>43800</v>
       </c>
       <c r="B409">
         <v>59.88</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410" s="3">
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
         <v>43831</v>
       </c>
       <c r="B410">
         <v>57.52</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411" s="3">
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
         <v>43862</v>
       </c>
       <c r="B411">
         <v>50.54</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412" s="3">
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
         <v>43891</v>
       </c>
       <c r="B412">
         <v>29.21</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413" s="3">
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
         <v>43922</v>
       </c>
       <c r="B413">
         <v>16.55</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" s="3">
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
         <v>43952</v>
       </c>
       <c r="B414">
         <v>28.56</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" s="3">
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
         <v>43983</v>
       </c>
       <c r="B415">
         <v>38.31</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416" s="3">
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
         <v>44013</v>
       </c>
       <c r="B416">
         <v>40.71</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417" s="3">
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
         <v>44044</v>
       </c>
       <c r="B417">
         <v>42.34</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418" s="3">
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
         <v>44075</v>
       </c>
       <c r="B418">
-        <v>39.630000000000003</v>
-      </c>
-    </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419" s="3">
+        <v>39.63</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
         <v>44105</v>
       </c>
       <c r="B419">
         <v>39.4</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420" s="3">
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
         <v>44136</v>
       </c>
       <c r="B420">
         <v>40.94</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421" s="3">
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
         <v>44166</v>
       </c>
       <c r="B421">
         <v>47.02</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" s="3">
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
         <v>44197</v>
       </c>
       <c r="B422">
         <v>52</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423" s="3">
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
         <v>44228</v>
       </c>
       <c r="B423">
         <v>59.04</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424" s="3">
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
         <v>44256</v>
       </c>
       <c r="B424">
         <v>62.33</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A425" s="3">
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
         <v>44287</v>
       </c>
       <c r="B425">
         <v>61.72</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A426" s="3">
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
         <v>44317</v>
       </c>
       <c r="B426">
         <v>65.17</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A427" s="3">
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
         <v>44348</v>
       </c>
       <c r="B427">
         <v>71.38</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A428" s="3">
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
         <v>44378</v>
       </c>
       <c r="B428">
-        <v>72.489999999999995</v>
-      </c>
-    </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A429" s="3">
+        <v>72.48999999999999</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
         <v>44409</v>
       </c>
       <c r="B429">
         <v>67.73</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A430" s="3">
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
         <v>44440</v>
       </c>
       <c r="B430">
-        <v>71.650000000000006</v>
-      </c>
-    </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A431" s="3">
+        <v>71.65000000000001</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
         <v>44470</v>
       </c>
       <c r="B431">
         <v>81.48</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A432" s="3">
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
         <v>44501</v>
       </c>
       <c r="B432">
-        <v>79.150000000000006</v>
-      </c>
-    </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A433" s="3">
+        <v>79.15000000000001</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
         <v>44531</v>
       </c>
       <c r="B433">
-        <v>71.709999999999994</v>
-      </c>
-    </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A434" s="3">
+        <v>71.70999999999999</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
         <v>44562</v>
       </c>
       <c r="B434">
         <v>83.22</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A435" s="3">
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
         <v>44593</v>
       </c>
       <c r="B435">
         <v>91.64</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A436" s="3">
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
         <v>44621</v>
       </c>
       <c r="B436">
         <v>108.5</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A437" s="3">
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
         <v>44652</v>
       </c>
       <c r="B437">
         <v>101.78</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A438" s="3">
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
         <v>44682</v>
       </c>
       <c r="B438">
         <v>109.55</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A439" s="3">
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
         <v>44713</v>
       </c>
       <c r="B439">
         <v>114.84</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A440" s="3">
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
         <v>44743</v>
       </c>
       <c r="B440">
         <v>101.62</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A441" s="3">
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
         <v>44774</v>
       </c>
       <c r="B441">
         <v>93.67</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A442" s="3">
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
         <v>44805</v>
       </c>
       <c r="B442">
-        <v>84.26</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A443" s="3">
+        <v>84.26000000000001</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
         <v>44835</v>
       </c>
       <c r="B443">
         <v>87.55</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A444" s="3">
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
         <v>44866</v>
       </c>
       <c r="B444">
         <v>84.37</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A445" s="3">
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
         <v>44896</v>
       </c>
       <c r="B445">
         <v>76.44</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A446" s="3">
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
         <v>44927</v>
       </c>
       <c r="B446">
         <v>78.12</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A447" s="3">
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
         <v>44958</v>
       </c>
       <c r="B447">
         <v>76.83</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A448" s="3">
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
         <v>44986</v>
       </c>
       <c r="B448">
         <v>73.28</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A449" s="3">
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
         <v>45017</v>
       </c>
       <c r="B449">
         <v>79.45</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A450" s="3">
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
         <v>45047</v>
       </c>
       <c r="B450">
         <v>71.58</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A451" s="3">
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
         <v>45078</v>
       </c>
       <c r="B451">
         <v>70.25</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A452" s="3">
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
         <v>45108</v>
       </c>
       <c r="B452">
-        <v>76.069999999999993</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A453" s="3">
+        <v>76.06999999999999</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
         <v>45139</v>
       </c>
       <c r="B453">
         <v>81.39</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A454" s="3">
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
         <v>45170</v>
       </c>
       <c r="B454">
-        <v>89.43</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A455" s="3">
+        <v>89.43000000000001</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
         <v>45200</v>
       </c>
       <c r="B455">
         <v>85.64</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A456" s="3">
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
         <v>45231</v>
       </c>
       <c r="B456">
         <v>77.69</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A457" s="3">
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
         <v>45261</v>
       </c>
       <c r="B457">
-        <v>71.900000000000006</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A458" s="3">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
         <v>45292</v>
       </c>
       <c r="B458">
-        <v>74.150000000000006</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A459" s="3">
+        <v>74.15000000000001</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
         <v>45323</v>
       </c>
       <c r="B459">
         <v>77.25</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A460" s="3">
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
         <v>45352</v>
       </c>
       <c r="B460">
         <v>81.28</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A461" s="3">
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
         <v>45383</v>
       </c>
       <c r="B461">
-        <v>85.35</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A462" s="3">
+        <v>85.34999999999999</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
         <v>45413</v>
       </c>
       <c r="B462">
         <v>80.02</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A463" s="3">
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
         <v>45444</v>
       </c>
       <c r="B463">
         <v>79.77</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A464" s="3">
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
         <v>45474</v>
       </c>
       <c r="B464">
         <v>81.8</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A465" s="3">
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
         <v>45505</v>
       </c>
       <c r="B465">
-        <v>76.680000000000007</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A466" s="3">
+        <v>76.68000000000001</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
         <v>45536</v>
       </c>
       <c r="B466">
-        <v>70.239999999999995</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A467" s="3">
+        <v>70.23999999999999</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
         <v>45566</v>
       </c>
       <c r="B467">
-        <v>71.989999999999995</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A468" s="3">
+        <v>71.98999999999999</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
         <v>45597</v>
       </c>
       <c r="B468">
         <v>69.95</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A469" s="3">
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
         <v>45627</v>
       </c>
       <c r="B469">
         <v>70.12</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A470" s="3">
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
         <v>45658</v>
       </c>
       <c r="B470">
-        <v>75.739999999999995</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A471" s="3">
+        <v>75.73999999999999</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
         <v>45689</v>
       </c>
       <c r="B471">
         <v>71.53</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A472" s="3">
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
         <v>45717</v>
       </c>
       <c r="B472">
-        <v>68.239999999999995</v>
-      </c>
-    </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A473" s="3">
+        <v>68.23999999999999</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
         <v>45748</v>
       </c>
       <c r="B473">
         <v>63.54</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A474" s="3">
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
         <v>45778</v>
       </c>
       <c r="B474">
         <v>62.17</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A475" s="3">
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
         <v>45809</v>
       </c>
       <c r="B475">
         <v>68.17</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A476" s="3">
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
         <v>45839</v>
       </c>
       <c r="B476">
         <v>68.39</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B477">
+        <v>64.86</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B478">
+        <v>63.96</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B479">
+        <v>60.89</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B480">
+        <v>60.06</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B481">
+        <v>57.97</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B482">
+        <v>60.04</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B483">
+        <v>64.51000000000001</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B484">
+        <v>91.38</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B485">
+        <v>100.32</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B486">
+        <v>102.13</v>
       </c>
     </row>
   </sheetData>
